--- a/pipeline/credit_rating/output/xhtn_tong_hop_20260921.xlsx
+++ b/pipeline/credit_rating/output/xhtn_tong_hop_20260921.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1329,7 +1329,7 @@
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -1983,7 +1983,7 @@
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2209,7 +2209,7 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:47</t>
+          <t>2026-09-21 10:07:16</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:47</t>
+          <t>2026-09-21 10:07:16</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:47</t>
+          <t>2026-09-21 10:07:16</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:49</t>
+          <t>2026-09-21 10:07:18</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:47</t>
+          <t>2026-09-21 10:07:16</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -10585,7 +10585,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -11737,7 +11737,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -13133,7 +13133,7 @@
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:47</t>
+          <t>2026-09-21 10:07:16</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -13597,7 +13597,7 @@
       <c r="AD115" t="inlineStr"/>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:49</t>
+          <t>2026-09-21 10:07:18</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -13957,7 +13957,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -14077,7 +14077,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -14759,7 +14759,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -14995,7 +14995,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -15107,7 +15107,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -15223,7 +15223,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -15563,7 +15563,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -15911,7 +15911,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -16137,7 +16137,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:49</t>
+          <t>2026-09-21 10:07:18</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -16361,7 +16361,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -16475,7 +16475,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -16703,7 +16703,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:47</t>
+          <t>2026-09-21 10:07:16</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -16923,7 +16923,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -17147,7 +17147,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -17261,7 +17261,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -17517,7 +17517,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -17627,7 +17627,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -17737,7 +17737,7 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -17857,7 +17857,7 @@
       </c>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -17971,7 +17971,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -18081,7 +18081,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -18331,7 +18331,7 @@
       <c r="AD156" t="inlineStr"/>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -18459,7 +18459,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -18703,7 +18703,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -18835,7 +18835,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -19071,7 +19071,7 @@
       <c r="AD162" t="inlineStr"/>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -19509,7 +19509,7 @@
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -19625,7 +19625,7 @@
       </c>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -19753,7 +19753,7 @@
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -19863,7 +19863,7 @@
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -19977,7 +19977,7 @@
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -20091,7 +20091,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -20205,7 +20205,7 @@
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -20315,7 +20315,7 @@
       </c>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -20429,7 +20429,7 @@
       </c>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -20767,7 +20767,7 @@
       </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -20883,7 +20883,7 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -20995,7 +20995,7 @@
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -21107,7 +21107,7 @@
       </c>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -21235,7 +21235,7 @@
       </c>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:49</t>
+          <t>2026-09-21 10:07:18</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -21345,7 +21345,7 @@
       </c>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -21465,7 +21465,7 @@
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -21587,7 +21587,7 @@
       <c r="AD184" t="inlineStr"/>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -21713,7 +21713,7 @@
       <c r="AD185" t="inlineStr"/>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -21839,7 +21839,7 @@
       <c r="AD186" t="inlineStr"/>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -21955,7 +21955,7 @@
       </c>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -22069,7 +22069,7 @@
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -22183,7 +22183,7 @@
       </c>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -22297,7 +22297,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -22417,7 +22417,7 @@
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -22537,7 +22537,7 @@
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -22647,7 +22647,7 @@
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -22867,7 +22867,7 @@
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -22983,7 +22983,7 @@
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -23111,7 +23111,7 @@
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -23223,7 +23223,7 @@
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -23335,7 +23335,7 @@
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -23453,7 +23453,7 @@
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:47</t>
+          <t>2026-09-21 10:07:16</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -23563,7 +23563,7 @@
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -23673,7 +23673,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -23785,7 +23785,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -23895,7 +23895,7 @@
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -24015,7 +24015,7 @@
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -24131,7 +24131,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -24247,7 +24247,7 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -24375,7 +24375,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -24487,7 +24487,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -24711,7 +24711,7 @@
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -24937,7 +24937,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -25057,7 +25057,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -25167,7 +25167,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -25287,7 +25287,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -25397,7 +25397,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -25511,7 +25511,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:47</t>
+          <t>2026-09-21 10:07:16</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -25621,7 +25621,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -25731,7 +25731,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -25845,7 +25845,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -25955,7 +25955,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -26177,7 +26177,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -26297,7 +26297,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -26409,7 +26409,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -26519,7 +26519,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -26643,7 +26643,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:49</t>
+          <t>2026-09-21 10:07:18</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -26767,7 +26767,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:49</t>
+          <t>2026-09-21 10:07:18</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -26987,7 +26987,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -27097,7 +27097,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -27209,7 +27209,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -27319,7 +27319,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -27429,7 +27429,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -27557,7 +27557,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -27663,7 +27663,7 @@
       </c>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -27775,7 +27775,7 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -27891,7 +27891,7 @@
       </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -28007,7 +28007,7 @@
       </c>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -28117,7 +28117,7 @@
       </c>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -28227,7 +28227,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -28343,7 +28343,7 @@
       </c>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -28459,7 +28459,7 @@
       </c>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -28685,7 +28685,7 @@
       </c>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -28801,7 +28801,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -28911,7 +28911,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -29021,7 +29021,7 @@
       </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -29131,7 +29131,7 @@
       </c>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -29231,7 +29231,7 @@
       </c>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -29347,7 +29347,7 @@
       </c>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -29457,7 +29457,7 @@
       </c>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -29569,7 +29569,7 @@
       </c>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -29679,7 +29679,7 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -29799,7 +29799,7 @@
       </c>
       <c r="AE256" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -29911,7 +29911,7 @@
       </c>
       <c r="AE257" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -30021,7 +30021,7 @@
       </c>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -30133,7 +30133,7 @@
       </c>
       <c r="AE259" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -30249,7 +30249,7 @@
       </c>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -30361,7 +30361,7 @@
       </c>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -30471,7 +30471,7 @@
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -30587,7 +30587,7 @@
       </c>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -30697,7 +30697,7 @@
       </c>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -30823,7 +30823,7 @@
       <c r="AD265" t="inlineStr"/>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -30951,7 +30951,7 @@
       </c>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -31063,7 +31063,7 @@
       </c>
       <c r="AE267" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -31163,7 +31163,7 @@
       </c>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -31263,7 +31263,7 @@
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -31377,7 +31377,7 @@
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -31491,7 +31491,7 @@
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -31591,7 +31591,7 @@
       </c>
       <c r="AE272" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -31711,7 +31711,7 @@
       </c>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -31823,7 +31823,7 @@
       </c>
       <c r="AE274" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -31935,7 +31935,7 @@
       </c>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -32049,7 +32049,7 @@
       </c>
       <c r="AE276" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -32163,7 +32163,7 @@
       </c>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:47</t>
+          <t>2026-09-21 10:07:16</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="AE278" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:47</t>
+          <t>2026-09-21 10:07:16</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -32409,7 +32409,7 @@
       </c>
       <c r="AE279" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -32537,7 +32537,7 @@
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -32665,7 +32665,7 @@
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -32793,7 +32793,7 @@
       </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -32905,7 +32905,7 @@
       </c>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -33017,7 +33017,7 @@
       </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -33127,7 +33127,7 @@
       </c>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -33237,7 +33237,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -33365,7 +33365,7 @@
       </c>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -33475,7 +33475,7 @@
       </c>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -33603,7 +33603,7 @@
       </c>
       <c r="AE289" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -33715,7 +33715,7 @@
       </c>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -33827,7 +33827,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -33937,7 +33937,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -34057,7 +34057,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -34181,7 +34181,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -34305,7 +34305,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -34429,7 +34429,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -34541,7 +34541,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -34657,7 +34657,7 @@
       </c>
       <c r="AE298" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -34769,7 +34769,7 @@
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:49</t>
+          <t>2026-09-21 10:07:18</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -34897,7 +34897,7 @@
       </c>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:49</t>
+          <t>2026-09-21 10:07:18</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -35025,7 +35025,7 @@
       </c>
       <c r="AE301" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -35137,7 +35137,7 @@
       </c>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -35249,7 +35249,7 @@
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -35359,7 +35359,7 @@
       </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -35469,7 +35469,7 @@
       </c>
       <c r="AE305" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -35585,7 +35585,7 @@
       </c>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -35697,7 +35697,7 @@
       </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -35817,7 +35817,7 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -35945,7 +35945,7 @@
       </c>
       <c r="AE309" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -36061,7 +36061,7 @@
       </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -36161,7 +36161,7 @@
       </c>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -36273,7 +36273,7 @@
       </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -36401,7 +36401,7 @@
       </c>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -36525,7 +36525,7 @@
       </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:49</t>
+          <t>2026-09-21 10:07:18</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -36637,7 +36637,7 @@
       </c>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -36747,7 +36747,7 @@
       </c>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -36857,7 +36857,7 @@
       </c>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -36967,7 +36967,7 @@
       </c>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -37077,7 +37077,7 @@
       </c>
       <c r="AE319" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -37197,7 +37197,7 @@
       </c>
       <c r="AE320" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -37307,7 +37307,7 @@
       </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -37417,7 +37417,7 @@
       </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -37527,7 +37527,7 @@
       </c>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -37647,7 +37647,7 @@
       </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -37767,7 +37767,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -37887,7 +37887,7 @@
       </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -38007,7 +38007,7 @@
       </c>
       <c r="AE327" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -38123,7 +38123,7 @@
       </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -38239,7 +38239,7 @@
       </c>
       <c r="AE329" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -38355,7 +38355,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -38467,7 +38467,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -38583,7 +38583,7 @@
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -38703,7 +38703,7 @@
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -38815,7 +38815,7 @@
       </c>
       <c r="AE334" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -38931,7 +38931,7 @@
       </c>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -39047,7 +39047,7 @@
       </c>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -39163,7 +39163,7 @@
       </c>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -39279,7 +39279,7 @@
       </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -39393,7 +39393,7 @@
       </c>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:47</t>
+          <t>2026-09-21 10:07:16</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -39509,7 +39509,7 @@
       </c>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -39625,7 +39625,7 @@
       </c>
       <c r="AE341" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -39741,7 +39741,7 @@
       </c>
       <c r="AE342" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -39851,7 +39851,7 @@
       </c>
       <c r="AE343" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -39967,7 +39967,7 @@
       </c>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -40079,7 +40079,7 @@
       </c>
       <c r="AE345" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -40189,7 +40189,7 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -40301,7 +40301,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -40413,7 +40413,7 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -40525,7 +40525,7 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -40645,7 +40645,7 @@
       </c>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -40773,7 +40773,7 @@
       </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -40893,7 +40893,7 @@
       </c>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -41021,7 +41021,7 @@
       </c>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -41243,7 +41243,7 @@
       </c>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -41353,7 +41353,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -41465,7 +41465,7 @@
       </c>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -41577,7 +41577,7 @@
       </c>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -41687,7 +41687,7 @@
       </c>
       <c r="AE359" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -41803,7 +41803,7 @@
       </c>
       <c r="AE360" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -41913,7 +41913,7 @@
       </c>
       <c r="AE361" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -42025,7 +42025,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -42135,7 +42135,7 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -42245,7 +42245,7 @@
       </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -42373,7 +42373,7 @@
       </c>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -42485,7 +42485,7 @@
       </c>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -42613,7 +42613,7 @@
       </c>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -42725,7 +42725,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -42835,7 +42835,7 @@
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -42945,7 +42945,7 @@
       </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -43055,7 +43055,7 @@
       </c>
       <c r="AE371" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -43167,7 +43167,7 @@
       </c>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -43277,7 +43277,7 @@
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -43405,7 +43405,7 @@
       </c>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -43517,7 +43517,7 @@
       </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -43627,7 +43627,7 @@
       </c>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -43737,7 +43737,7 @@
       </c>
       <c r="AE377" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -43847,7 +43847,7 @@
       </c>
       <c r="AE378" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -43957,7 +43957,7 @@
       </c>
       <c r="AE379" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -44067,7 +44067,7 @@
       </c>
       <c r="AE380" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -44179,7 +44179,7 @@
       </c>
       <c r="AE381" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -44307,7 +44307,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -44417,7 +44417,7 @@
       </c>
       <c r="AE383" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -44527,7 +44527,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -44639,7 +44639,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:49</t>
+          <t>2026-09-21 10:07:18</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -44749,7 +44749,7 @@
       </c>
       <c r="AE386" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -44861,7 +44861,7 @@
       </c>
       <c r="AE387" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -44989,7 +44989,7 @@
       </c>
       <c r="AE388" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -45099,7 +45099,7 @@
       </c>
       <c r="AE389" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -45211,7 +45211,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -45321,7 +45321,7 @@
       </c>
       <c r="AE391" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -45431,7 +45431,7 @@
       </c>
       <c r="AE392" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -45541,7 +45541,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="AE394" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -45751,7 +45751,7 @@
       </c>
       <c r="AE395" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -45851,7 +45851,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -45961,7 +45961,7 @@
       </c>
       <c r="AE397" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -46089,7 +46089,7 @@
       </c>
       <c r="AE398" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -46199,7 +46199,7 @@
       </c>
       <c r="AE399" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -46309,7 +46309,7 @@
       </c>
       <c r="AE400" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -46419,7 +46419,7 @@
       </c>
       <c r="AE401" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -46529,7 +46529,7 @@
       </c>
       <c r="AE402" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -46639,7 +46639,7 @@
       </c>
       <c r="AE403" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -46749,7 +46749,7 @@
       </c>
       <c r="AE404" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -46859,7 +46859,7 @@
       </c>
       <c r="AE405" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -46969,7 +46969,7 @@
       </c>
       <c r="AE406" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -47097,7 +47097,7 @@
       </c>
       <c r="AE407" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -47209,7 +47209,7 @@
       </c>
       <c r="AE408" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -47309,7 +47309,7 @@
       </c>
       <c r="AE409" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -47419,7 +47419,7 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -47533,7 +47533,7 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -47643,7 +47643,7 @@
       </c>
       <c r="AE412" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -47743,7 +47743,7 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -47855,7 +47855,7 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -47967,7 +47967,7 @@
       </c>
       <c r="AE415" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -48077,7 +48077,7 @@
       </c>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="AE417" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -48301,7 +48301,7 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -48411,7 +48411,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -48539,7 +48539,7 @@
       </c>
       <c r="AE420" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -48671,7 +48671,7 @@
       </c>
       <c r="AE421" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -48803,7 +48803,7 @@
       </c>
       <c r="AE422" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -48935,7 +48935,7 @@
       </c>
       <c r="AE423" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -49059,7 +49059,7 @@
       </c>
       <c r="AE424" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:49</t>
+          <t>2026-09-21 10:07:18</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -49171,7 +49171,7 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -49271,7 +49271,7 @@
       </c>
       <c r="AE426" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -49391,7 +49391,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -49507,7 +49507,7 @@
       </c>
       <c r="AE428" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -49619,7 +49619,7 @@
       </c>
       <c r="AE429" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -49741,7 +49741,7 @@
       <c r="AD430" t="inlineStr"/>
       <c r="AE430" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -49853,7 +49853,7 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -49963,7 +49963,7 @@
       </c>
       <c r="AE432" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -50073,7 +50073,7 @@
       </c>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -50183,7 +50183,7 @@
       </c>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -50293,7 +50293,7 @@
       </c>
       <c r="AE435" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -50421,7 +50421,7 @@
       </c>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -50537,7 +50537,7 @@
       </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -50647,7 +50647,7 @@
       </c>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -50775,7 +50775,7 @@
       </c>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -50903,7 +50903,7 @@
       </c>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -51031,7 +51031,7 @@
       </c>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -51159,7 +51159,7 @@
       </c>
       <c r="AE442" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -51271,7 +51271,7 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -51381,7 +51381,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -51509,7 +51509,7 @@
       </c>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -51621,7 +51621,7 @@
       </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -51733,7 +51733,7 @@
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -51849,7 +51849,7 @@
       </c>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -51961,7 +51961,7 @@
       </c>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -52073,7 +52073,7 @@
       </c>
       <c r="AE450" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -52185,7 +52185,7 @@
       </c>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -52297,7 +52297,7 @@
       </c>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -52417,7 +52417,7 @@
       </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -52527,7 +52527,7 @@
       </c>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -52655,7 +52655,7 @@
       </c>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -52775,7 +52775,7 @@
       </c>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -52887,7 +52887,7 @@
       </c>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -52999,7 +52999,7 @@
       </c>
       <c r="AE458" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -53099,7 +53099,7 @@
       </c>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -53215,7 +53215,7 @@
       </c>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -53325,7 +53325,7 @@
       </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -53437,7 +53437,7 @@
       </c>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -53547,7 +53547,7 @@
       </c>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
@@ -53659,7 +53659,7 @@
       </c>
       <c r="AE464" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF464" t="inlineStr">
@@ -53771,7 +53771,7 @@
       </c>
       <c r="AE465" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF465" t="inlineStr">
@@ -53871,7 +53871,7 @@
       </c>
       <c r="AE466" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF466" t="inlineStr">
@@ -53981,7 +53981,7 @@
       </c>
       <c r="AE467" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF467" t="inlineStr">
@@ -54093,7 +54093,7 @@
       </c>
       <c r="AE468" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF468" t="inlineStr">
@@ -54203,7 +54203,7 @@
       </c>
       <c r="AE469" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF469" t="inlineStr">
@@ -54313,7 +54313,7 @@
       </c>
       <c r="AE470" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF470" t="inlineStr">
@@ -54425,7 +54425,7 @@
       </c>
       <c r="AE471" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF471" t="inlineStr">
@@ -54535,7 +54535,7 @@
       </c>
       <c r="AE472" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF472" t="inlineStr">
@@ -54645,7 +54645,7 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF473" t="inlineStr">
@@ -54755,7 +54755,7 @@
       </c>
       <c r="AE474" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF474" t="inlineStr">
@@ -54875,7 +54875,7 @@
       </c>
       <c r="AE475" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF475" t="inlineStr">
@@ -54999,7 +54999,7 @@
       </c>
       <c r="AE476" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:49</t>
+          <t>2026-09-21 10:07:18</t>
         </is>
       </c>
       <c r="AF476" t="inlineStr">
@@ -55109,7 +55109,7 @@
       </c>
       <c r="AE477" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF477" t="inlineStr">
@@ -55221,7 +55221,7 @@
       </c>
       <c r="AE478" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF478" t="inlineStr">
@@ -55331,7 +55331,7 @@
       </c>
       <c r="AE479" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF479" t="inlineStr">
@@ -55443,7 +55443,7 @@
       </c>
       <c r="AE480" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF480" t="inlineStr">
@@ -55555,7 +55555,7 @@
       </c>
       <c r="AE481" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF481" t="inlineStr">
@@ -55665,7 +55665,7 @@
       </c>
       <c r="AE482" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF482" t="inlineStr">
@@ -55775,7 +55775,7 @@
       </c>
       <c r="AE483" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF483" t="inlineStr">
@@ -55885,7 +55885,7 @@
       </c>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF484" t="inlineStr">
@@ -55995,7 +55995,7 @@
       </c>
       <c r="AE485" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF485" t="inlineStr">
@@ -56105,7 +56105,7 @@
       </c>
       <c r="AE486" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF486" t="inlineStr">
@@ -56215,7 +56215,7 @@
       </c>
       <c r="AE487" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF487" t="inlineStr">
@@ -56327,7 +56327,7 @@
       </c>
       <c r="AE488" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF488" t="inlineStr">
@@ -56439,7 +56439,7 @@
       </c>
       <c r="AE489" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF489" t="inlineStr">
@@ -56551,7 +56551,7 @@
       </c>
       <c r="AE490" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF490" t="inlineStr">
@@ -56661,7 +56661,7 @@
       </c>
       <c r="AE491" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF491" t="inlineStr">
@@ -56773,7 +56773,7 @@
       </c>
       <c r="AE492" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF492" t="inlineStr">
@@ -56873,7 +56873,7 @@
       </c>
       <c r="AE493" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF493" t="inlineStr">
@@ -56983,7 +56983,7 @@
       </c>
       <c r="AE494" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF494" t="inlineStr">
@@ -57083,7 +57083,7 @@
       </c>
       <c r="AE495" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF495" t="inlineStr">
@@ -57183,7 +57183,7 @@
       </c>
       <c r="AE496" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF496" t="inlineStr">
@@ -57295,7 +57295,7 @@
       </c>
       <c r="AE497" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF497" t="inlineStr">
@@ -57407,7 +57407,7 @@
       </c>
       <c r="AE498" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF498" t="inlineStr">
@@ -57519,7 +57519,7 @@
       </c>
       <c r="AE499" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF499" t="inlineStr">
@@ -57629,7 +57629,7 @@
       </c>
       <c r="AE500" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF500" t="inlineStr">
@@ -57739,7 +57739,7 @@
       </c>
       <c r="AE501" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF501" t="inlineStr">
@@ -57849,7 +57849,7 @@
       </c>
       <c r="AE502" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF502" t="inlineStr">
@@ -57961,7 +57961,7 @@
       </c>
       <c r="AE503" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF503" t="inlineStr">
@@ -58071,7 +58071,7 @@
       </c>
       <c r="AE504" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF504" t="inlineStr">
@@ -58181,7 +58181,7 @@
       </c>
       <c r="AE505" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF505" t="inlineStr">
@@ -58291,7 +58291,7 @@
       </c>
       <c r="AE506" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF506" t="inlineStr">
@@ -58401,7 +58401,7 @@
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
@@ -58513,7 +58513,7 @@
       </c>
       <c r="AE508" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF508" t="inlineStr">
@@ -58625,7 +58625,7 @@
       </c>
       <c r="AE509" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF509" t="inlineStr">
@@ -58741,7 +58741,7 @@
       </c>
       <c r="AE510" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF510" t="inlineStr">
@@ -58869,7 +58869,7 @@
       </c>
       <c r="AE511" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF511" t="inlineStr">
@@ -58981,7 +58981,7 @@
       </c>
       <c r="AE512" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF512" t="inlineStr">
@@ -59091,7 +59091,7 @@
       </c>
       <c r="AE513" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF513" t="inlineStr">
@@ -59211,7 +59211,7 @@
       </c>
       <c r="AE514" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF514" t="inlineStr">
@@ -59321,7 +59321,7 @@
       </c>
       <c r="AE515" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF515" t="inlineStr">
@@ -59431,7 +59431,7 @@
       </c>
       <c r="AE516" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF516" t="inlineStr">
@@ -59541,7 +59541,7 @@
       </c>
       <c r="AE517" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF517" t="inlineStr">
@@ -59661,7 +59661,7 @@
       </c>
       <c r="AE518" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF518" t="inlineStr">
@@ -59777,7 +59777,7 @@
       </c>
       <c r="AE519" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF519" t="inlineStr">
@@ -59889,7 +59889,7 @@
       </c>
       <c r="AE520" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF520" t="inlineStr">
@@ -60009,7 +60009,7 @@
       </c>
       <c r="AE521" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF521" t="inlineStr">
@@ -60121,7 +60121,7 @@
       </c>
       <c r="AE522" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF522" t="inlineStr">
@@ -60221,7 +60221,7 @@
       </c>
       <c r="AE523" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF523" t="inlineStr">
@@ -60341,7 +60341,7 @@
       </c>
       <c r="AE524" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF524" t="inlineStr">
@@ -60451,7 +60451,7 @@
       </c>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF525" t="inlineStr">
@@ -60563,7 +60563,7 @@
       </c>
       <c r="AE526" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF526" t="inlineStr">
@@ -60679,7 +60679,7 @@
       </c>
       <c r="AE527" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF527" t="inlineStr">
@@ -60791,7 +60791,7 @@
       </c>
       <c r="AE528" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF528" t="inlineStr">
@@ -60903,7 +60903,7 @@
       </c>
       <c r="AE529" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF529" t="inlineStr">
@@ -61031,7 +61031,7 @@
       </c>
       <c r="AE530" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF530" t="inlineStr">
@@ -61141,7 +61141,7 @@
       </c>
       <c r="AE531" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF531" t="inlineStr">
@@ -61251,7 +61251,7 @@
       </c>
       <c r="AE532" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF532" t="inlineStr">
@@ -61361,7 +61361,7 @@
       </c>
       <c r="AE533" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF533" t="inlineStr">
@@ -61473,7 +61473,7 @@
       </c>
       <c r="AE534" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF534" t="inlineStr">
@@ -61601,7 +61601,7 @@
       </c>
       <c r="AE535" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF535" t="inlineStr">
@@ -61713,7 +61713,7 @@
       </c>
       <c r="AE536" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF536" t="inlineStr">
@@ -61825,7 +61825,7 @@
       </c>
       <c r="AE537" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF537" t="inlineStr">
@@ -61937,7 +61937,7 @@
       </c>
       <c r="AE538" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF538" t="inlineStr">
@@ -62037,7 +62037,7 @@
       </c>
       <c r="AE539" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF539" t="inlineStr">
@@ -62147,7 +62147,7 @@
       </c>
       <c r="AE540" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF540" t="inlineStr">
@@ -62257,7 +62257,7 @@
       </c>
       <c r="AE541" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF541" t="inlineStr">
@@ -62357,7 +62357,7 @@
       </c>
       <c r="AE542" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF542" t="inlineStr">
@@ -62467,7 +62467,7 @@
       </c>
       <c r="AE543" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF543" t="inlineStr">
@@ -62595,7 +62595,7 @@
       </c>
       <c r="AE544" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF544" t="inlineStr">
@@ -62705,7 +62705,7 @@
       </c>
       <c r="AE545" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF545" t="inlineStr">
@@ -62817,7 +62817,7 @@
       </c>
       <c r="AE546" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF546" t="inlineStr">
@@ -62927,7 +62927,7 @@
       </c>
       <c r="AE547" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF547" t="inlineStr">
@@ -63039,7 +63039,7 @@
       </c>
       <c r="AE548" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF548" t="inlineStr">
@@ -63149,7 +63149,7 @@
       </c>
       <c r="AE549" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF549" t="inlineStr">
@@ -63259,7 +63259,7 @@
       </c>
       <c r="AE550" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF550" t="inlineStr">
@@ -63359,7 +63359,7 @@
       </c>
       <c r="AE551" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF551" t="inlineStr">
@@ -63469,7 +63469,7 @@
       </c>
       <c r="AE552" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF552" t="inlineStr">
@@ -63581,7 +63581,7 @@
       </c>
       <c r="AE553" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF553" t="inlineStr">
@@ -63691,7 +63691,7 @@
       </c>
       <c r="AE554" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF554" t="inlineStr">
@@ -63801,7 +63801,7 @@
       </c>
       <c r="AE555" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF555" t="inlineStr">
@@ -63911,7 +63911,7 @@
       </c>
       <c r="AE556" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF556" t="inlineStr">
@@ -64021,7 +64021,7 @@
       </c>
       <c r="AE557" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF557" t="inlineStr">
@@ -64131,7 +64131,7 @@
       </c>
       <c r="AE558" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF558" t="inlineStr">
@@ -64241,7 +64241,7 @@
       </c>
       <c r="AE559" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF559" t="inlineStr">
@@ -64341,7 +64341,7 @@
       </c>
       <c r="AE560" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF560" t="inlineStr">
@@ -64451,7 +64451,7 @@
       </c>
       <c r="AE561" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF561" t="inlineStr">
@@ -64561,7 +64561,7 @@
       </c>
       <c r="AE562" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF562" t="inlineStr">
@@ -64673,7 +64673,7 @@
       </c>
       <c r="AE563" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF563" t="inlineStr">
@@ -64783,7 +64783,7 @@
       </c>
       <c r="AE564" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF564" t="inlineStr">
@@ -64895,7 +64895,7 @@
       </c>
       <c r="AE565" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF565" t="inlineStr">
@@ -65005,7 +65005,7 @@
       </c>
       <c r="AE566" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF566" t="inlineStr">
@@ -65115,7 +65115,7 @@
       </c>
       <c r="AE567" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF567" t="inlineStr">
@@ -65225,7 +65225,7 @@
       </c>
       <c r="AE568" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF568" t="inlineStr">
@@ -65335,7 +65335,7 @@
       </c>
       <c r="AE569" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF569" t="inlineStr">
@@ -65445,7 +65445,7 @@
       </c>
       <c r="AE570" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF570" t="inlineStr">
@@ -65557,7 +65557,7 @@
       </c>
       <c r="AE571" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF571" t="inlineStr">
@@ -65667,7 +65667,7 @@
       </c>
       <c r="AE572" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF572" t="inlineStr">
@@ -65779,7 +65779,7 @@
       </c>
       <c r="AE573" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF573" t="inlineStr">
@@ -65891,7 +65891,7 @@
       </c>
       <c r="AE574" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF574" t="inlineStr">
@@ -66001,7 +66001,7 @@
       </c>
       <c r="AE575" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF575" t="inlineStr">
@@ -66113,7 +66113,7 @@
       </c>
       <c r="AE576" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF576" t="inlineStr">
@@ -66225,7 +66225,7 @@
       </c>
       <c r="AE577" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF577" t="inlineStr">
@@ -66335,7 +66335,7 @@
       </c>
       <c r="AE578" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF578" t="inlineStr">
@@ -66445,7 +66445,7 @@
       </c>
       <c r="AE579" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF579" t="inlineStr">
@@ -66555,7 +66555,7 @@
       </c>
       <c r="AE580" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF580" t="inlineStr">
@@ -66665,7 +66665,7 @@
       </c>
       <c r="AE581" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF581" t="inlineStr">
@@ -66765,7 +66765,7 @@
       </c>
       <c r="AE582" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF582" t="inlineStr">
@@ -66877,7 +66877,7 @@
       </c>
       <c r="AE583" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF583" t="inlineStr">
@@ -66987,7 +66987,7 @@
       </c>
       <c r="AE584" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF584" t="inlineStr">
@@ -67097,7 +67097,7 @@
       </c>
       <c r="AE585" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF585" t="inlineStr">
@@ -67225,7 +67225,7 @@
       </c>
       <c r="AE586" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF586" t="inlineStr">
@@ -67337,7 +67337,7 @@
       </c>
       <c r="AE587" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF587" t="inlineStr">
@@ -67449,7 +67449,7 @@
       </c>
       <c r="AE588" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF588" t="inlineStr">
@@ -67577,7 +67577,7 @@
       </c>
       <c r="AE589" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF589" t="inlineStr">
@@ -67689,7 +67689,7 @@
       </c>
       <c r="AE590" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF590" t="inlineStr">
@@ -67817,7 +67817,7 @@
       </c>
       <c r="AE591" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF591" t="inlineStr">
@@ -67945,7 +67945,7 @@
       </c>
       <c r="AE592" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="AF592" t="inlineStr">
@@ -68057,7 +68057,7 @@
       </c>
       <c r="AE593" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF593" t="inlineStr">
@@ -68169,7 +68169,7 @@
       </c>
       <c r="AE594" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF594" t="inlineStr">
@@ -68279,7 +68279,7 @@
       </c>
       <c r="AE595" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF595" t="inlineStr">
@@ -68391,7 +68391,7 @@
       </c>
       <c r="AE596" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF596" t="inlineStr">
@@ -68501,7 +68501,7 @@
       </c>
       <c r="AE597" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF597" t="inlineStr">
@@ -68611,7 +68611,7 @@
       </c>
       <c r="AE598" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF598" t="inlineStr">
@@ -68723,7 +68723,7 @@
       </c>
       <c r="AE599" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF599" t="inlineStr">
@@ -68835,7 +68835,7 @@
       </c>
       <c r="AE600" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF600" t="inlineStr">
@@ -68947,7 +68947,7 @@
       </c>
       <c r="AE601" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF601" t="inlineStr">
@@ -69057,7 +69057,7 @@
       </c>
       <c r="AE602" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF602" t="inlineStr">
@@ -69167,7 +69167,7 @@
       </c>
       <c r="AE603" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF603" t="inlineStr">
@@ -69279,7 +69279,7 @@
       </c>
       <c r="AE604" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF604" t="inlineStr">
@@ -69391,7 +69391,7 @@
       </c>
       <c r="AE605" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF605" t="inlineStr">
@@ -69501,7 +69501,7 @@
       </c>
       <c r="AE606" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF606" t="inlineStr">
@@ -69613,7 +69613,7 @@
       </c>
       <c r="AE607" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF607" t="inlineStr">
@@ -69723,7 +69723,7 @@
       </c>
       <c r="AE608" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF608" t="inlineStr">
@@ -69823,7 +69823,7 @@
       </c>
       <c r="AE609" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF609" t="inlineStr">
@@ -69933,7 +69933,7 @@
       </c>
       <c r="AE610" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF610" t="inlineStr">
@@ -70045,7 +70045,7 @@
       </c>
       <c r="AE611" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF611" t="inlineStr">
@@ -70155,7 +70155,7 @@
       </c>
       <c r="AE612" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF612" t="inlineStr">
@@ -70267,7 +70267,7 @@
       </c>
       <c r="AE613" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF613" t="inlineStr">
@@ -70377,7 +70377,7 @@
       </c>
       <c r="AE614" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF614" t="inlineStr">
@@ -70487,7 +70487,7 @@
       </c>
       <c r="AE615" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF615" t="inlineStr">
@@ -70597,7 +70597,7 @@
       </c>
       <c r="AE616" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF616" t="inlineStr">
@@ -70707,7 +70707,7 @@
       </c>
       <c r="AE617" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF617" t="inlineStr">
@@ -70817,7 +70817,7 @@
       </c>
       <c r="AE618" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF618" t="inlineStr">
@@ -70929,7 +70929,7 @@
       </c>
       <c r="AE619" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF619" t="inlineStr">
@@ -71039,7 +71039,7 @@
       </c>
       <c r="AE620" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF620" t="inlineStr">
@@ -71149,7 +71149,7 @@
       </c>
       <c r="AE621" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF621" t="inlineStr">
@@ -71259,7 +71259,7 @@
       </c>
       <c r="AE622" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF622" t="inlineStr">
@@ -71371,7 +71371,7 @@
       </c>
       <c r="AE623" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF623" t="inlineStr">
@@ -71481,7 +71481,7 @@
       </c>
       <c r="AE624" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF624" t="inlineStr">
@@ -71593,7 +71593,7 @@
       </c>
       <c r="AE625" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF625" t="inlineStr">
@@ -71705,7 +71705,7 @@
       </c>
       <c r="AE626" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF626" t="inlineStr">
@@ -71805,7 +71805,7 @@
       </c>
       <c r="AE627" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF627" t="inlineStr">
@@ -71915,7 +71915,7 @@
       </c>
       <c r="AE628" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF628" t="inlineStr">
@@ -72027,7 +72027,7 @@
       </c>
       <c r="AE629" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF629" t="inlineStr">
@@ -72139,7 +72139,7 @@
       </c>
       <c r="AE630" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF630" t="inlineStr">
@@ -72251,7 +72251,7 @@
       </c>
       <c r="AE631" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF631" t="inlineStr">
@@ -72363,7 +72363,7 @@
       </c>
       <c r="AE632" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF632" t="inlineStr">
@@ -72473,7 +72473,7 @@
       </c>
       <c r="AE633" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF633" t="inlineStr">
@@ -72583,7 +72583,7 @@
       </c>
       <c r="AE634" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF634" t="inlineStr">
@@ -72695,7 +72695,7 @@
       </c>
       <c r="AE635" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF635" t="inlineStr">
@@ -72805,7 +72805,7 @@
       </c>
       <c r="AE636" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF636" t="inlineStr">
@@ -72917,7 +72917,7 @@
       </c>
       <c r="AE637" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF637" t="inlineStr">
@@ -73017,7 +73017,7 @@
       </c>
       <c r="AE638" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF638" t="inlineStr">
@@ -73127,7 +73127,7 @@
       </c>
       <c r="AE639" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF639" t="inlineStr">
@@ -73239,7 +73239,7 @@
       </c>
       <c r="AE640" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF640" t="inlineStr">
@@ -73349,7 +73349,7 @@
       <c r="AD641" t="inlineStr"/>
       <c r="AE641" t="inlineStr">
         <is>
-          <t>2026-09-21 09:16:02</t>
+          <t>2026-09-21 10:07:32</t>
         </is>
       </c>
       <c r="AF641" t="inlineStr">
@@ -73461,7 +73461,7 @@
       </c>
       <c r="AE642" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF642" t="inlineStr">
@@ -73573,7 +73573,7 @@
       </c>
       <c r="AE643" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF643" t="inlineStr">
@@ -73683,7 +73683,7 @@
       </c>
       <c r="AE644" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF644" t="inlineStr">
@@ -73795,7 +73795,7 @@
       </c>
       <c r="AE645" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF645" t="inlineStr">
@@ -73895,7 +73895,7 @@
       </c>
       <c r="AE646" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF646" t="inlineStr">
@@ -73995,7 +73995,7 @@
       </c>
       <c r="AE647" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF647" t="inlineStr">
@@ -74095,7 +74095,7 @@
       </c>
       <c r="AE648" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF648" t="inlineStr">
@@ -74207,7 +74207,7 @@
       </c>
       <c r="AE649" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF649" t="inlineStr">
@@ -74307,7 +74307,7 @@
       </c>
       <c r="AE650" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF650" t="inlineStr">
@@ -74417,7 +74417,7 @@
       </c>
       <c r="AE651" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF651" t="inlineStr">
@@ -74517,7 +74517,7 @@
       </c>
       <c r="AE652" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF652" t="inlineStr">
@@ -74629,7 +74629,7 @@
       </c>
       <c r="AE653" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF653" t="inlineStr">
@@ -74741,7 +74741,7 @@
       </c>
       <c r="AE654" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF654" t="inlineStr">
@@ -74853,7 +74853,7 @@
       </c>
       <c r="AE655" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF655" t="inlineStr">
@@ -74965,7 +74965,7 @@
       </c>
       <c r="AE656" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF656" t="inlineStr">
@@ -75065,7 +75065,7 @@
       </c>
       <c r="AE657" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF657" t="inlineStr">
@@ -75177,7 +75177,7 @@
       </c>
       <c r="AE658" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF658" t="inlineStr">
@@ -75287,7 +75287,7 @@
       </c>
       <c r="AE659" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF659" t="inlineStr">
@@ -75399,7 +75399,7 @@
       </c>
       <c r="AE660" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF660" t="inlineStr">
@@ -75499,7 +75499,7 @@
       </c>
       <c r="AE661" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF661" t="inlineStr">
@@ -75599,7 +75599,7 @@
       </c>
       <c r="AE662" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF662" t="inlineStr">
@@ -75699,7 +75699,7 @@
       </c>
       <c r="AE663" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF663" t="inlineStr">
@@ -75799,7 +75799,7 @@
       </c>
       <c r="AE664" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF664" t="inlineStr">
@@ -75911,7 +75911,7 @@
       </c>
       <c r="AE665" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF665" t="inlineStr">
@@ -76023,7 +76023,7 @@
       </c>
       <c r="AE666" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF666" t="inlineStr">
@@ -76123,7 +76123,7 @@
       </c>
       <c r="AE667" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF667" t="inlineStr">
@@ -76233,7 +76233,7 @@
       </c>
       <c r="AE668" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF668" t="inlineStr">
@@ -76345,7 +76345,7 @@
       </c>
       <c r="AE669" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF669" t="inlineStr">
@@ -76457,7 +76457,7 @@
       </c>
       <c r="AE670" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF670" t="inlineStr">
@@ -76569,7 +76569,7 @@
       </c>
       <c r="AE671" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF671" t="inlineStr">
@@ -76681,7 +76681,7 @@
       </c>
       <c r="AE672" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF672" t="inlineStr">
@@ -76793,7 +76793,7 @@
       </c>
       <c r="AE673" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF673" t="inlineStr">
@@ -76905,7 +76905,7 @@
       </c>
       <c r="AE674" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF674" t="inlineStr">
@@ -77017,7 +77017,7 @@
       </c>
       <c r="AE675" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF675" t="inlineStr">
@@ -77117,7 +77117,7 @@
       </c>
       <c r="AE676" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF676" t="inlineStr">
@@ -77217,7 +77217,7 @@
       </c>
       <c r="AE677" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF677" t="inlineStr">
@@ -77329,7 +77329,7 @@
       </c>
       <c r="AE678" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:33</t>
+          <t>2026-09-21 10:07:01</t>
         </is>
       </c>
       <c r="AF678" t="inlineStr">
@@ -77429,7 +77429,7 @@
       </c>
       <c r="AE679" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF679" t="inlineStr">
@@ -77529,7 +77529,7 @@
       </c>
       <c r="AE680" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF680" t="inlineStr">
@@ -77629,7 +77629,7 @@
       </c>
       <c r="AE681" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF681" t="inlineStr">
@@ -77739,7 +77739,7 @@
       </c>
       <c r="AE682" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF682" t="inlineStr">
@@ -77839,7 +77839,7 @@
       </c>
       <c r="AE683" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF683" t="inlineStr">
@@ -77949,7 +77949,7 @@
       </c>
       <c r="AE684" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF684" t="inlineStr">
@@ -78031,7 +78031,7 @@
       <c r="AD685" t="inlineStr"/>
       <c r="AE685" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF685" t="inlineStr">
@@ -78113,7 +78113,7 @@
       <c r="AD686" t="inlineStr"/>
       <c r="AE686" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF686" t="inlineStr">
@@ -78195,7 +78195,7 @@
       <c r="AD687" t="inlineStr"/>
       <c r="AE687" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF687" t="inlineStr">
@@ -78277,7 +78277,7 @@
       <c r="AD688" t="inlineStr"/>
       <c r="AE688" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:42</t>
+          <t>2026-09-21 10:07:11</t>
         </is>
       </c>
       <c r="AF688" t="inlineStr">
